--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.92881538865689</v>
+        <v>5.188432500656745</v>
       </c>
       <c r="D2" t="n">
-        <v>32.88885041000872</v>
+        <v>5.344438191626417</v>
       </c>
       <c r="E2" t="n">
-        <v>11.89620242725131</v>
+        <v>1.933132894428339</v>
       </c>
       <c r="F2" t="n">
-        <v>11.61469401911576</v>
+        <v>1.887387778106311</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.234237107146</v>
+        <v>4.100563529911226</v>
       </c>
       <c r="D3" t="n">
-        <v>26.1044847302802</v>
+        <v>4.241978768670533</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89620242725131</v>
+        <v>1.933132894428339</v>
       </c>
       <c r="F3" t="n">
-        <v>11.61469401911576</v>
+        <v>1.887387778106311</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.99609355256075</v>
+        <v>5.686865202291123</v>
       </c>
       <c r="D4" t="n">
-        <v>35.19326289839074</v>
+        <v>5.718905220988495</v>
       </c>
       <c r="E4" t="n">
-        <v>11.89620242725131</v>
+        <v>1.933132894428339</v>
       </c>
       <c r="F4" t="n">
-        <v>11.61469401911576</v>
+        <v>1.887387778106311</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.68579689529091</v>
+        <v>9.373941995484774</v>
       </c>
       <c r="D5" t="n">
-        <v>57.48781959231063</v>
+        <v>9.341770683750477</v>
       </c>
       <c r="E5" t="n">
-        <v>11.89620242725131</v>
+        <v>1.933132894428339</v>
       </c>
       <c r="F5" t="n">
-        <v>11.61469401911576</v>
+        <v>1.887387778106311</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.50297870537734</v>
+        <v>9.019234039623818</v>
       </c>
       <c r="D6" t="n">
-        <v>55.07890797312286</v>
+        <v>8.950322545632465</v>
       </c>
       <c r="E6" t="n">
-        <v>11.89620242725131</v>
+        <v>1.933132894428339</v>
       </c>
       <c r="F6" t="n">
-        <v>11.61469401911576</v>
+        <v>1.887387778106311</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.49064172190263</v>
+        <v>4.629729279809177</v>
       </c>
       <c r="D7" t="n">
-        <v>27.80365752418144</v>
+        <v>4.518094347679485</v>
       </c>
       <c r="E7" t="n">
-        <v>11.89620242725131</v>
+        <v>1.933132894428339</v>
       </c>
       <c r="F7" t="n">
-        <v>11.61469401911576</v>
+        <v>1.887387778106311</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.8927680770118</v>
+        <v>6.645074812514418</v>
       </c>
       <c r="D8" t="n">
-        <v>39.88580201184723</v>
+        <v>6.481442826925174</v>
       </c>
       <c r="E8" t="n">
-        <v>11.89620242725131</v>
+        <v>1.933132894428339</v>
       </c>
       <c r="F8" t="n">
-        <v>11.61469401911576</v>
+        <v>1.887387778106311</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
